--- a/data/trans_orig/IP31KM02_R_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM02_R_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>84144</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>73861</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>92893</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>69,42%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>60,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>76,64%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>69662</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>61387</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>77440</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>68,49%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60,36%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>76,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>95003</t>
+          <t>68243</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85068</t>
+          <t>58943</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104651</t>
+          <t>75028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>164665</t>
+          <t>152386</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>151473</t>
+          <t>139617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>176826</t>
+          <t>162866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>73,51%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>37065</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>28316</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>47348</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30,58%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>23,36%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>32047</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24269</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>40322</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>31,51%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39,64%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40173</t>
+          <t>32106</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30525</t>
+          <t>25321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50108</t>
+          <t>41406</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>72221</t>
+          <t>69172</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60060</t>
+          <t>58692</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85413</t>
+          <t>81941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,98%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>59486</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>50899</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>66822</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>66,18%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>56,63%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>74,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>59568</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>51112</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>66944</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>63,78%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>54,73%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>71,68%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60821</t>
+          <t>61375</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51820</t>
+          <t>53485</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68737</t>
+          <t>68845</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>120390</t>
+          <t>120861</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108884</t>
+          <t>108262</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130406</t>
+          <t>131330</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>70,88%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30394</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23058</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>38981</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>33,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>25,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>43,37%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>33824</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>26448</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>42280</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>36,22%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>45,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>32887</t>
+          <t>34035</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24971</t>
+          <t>26565</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41888</t>
+          <t>41925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>66711</t>
+          <t>64429</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56695</t>
+          <t>53960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>78217</t>
+          <t>77028</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,57%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37578</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>31521</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43168</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>67,29%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>56,45%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>77,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>33693</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26743</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39259</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>67,27%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>53,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>78,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40281</t>
+          <t>34518</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32987</t>
+          <t>26837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47016</t>
+          <t>40446</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>73974</t>
+          <t>72096</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63271</t>
+          <t>62385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82207</t>
+          <t>80148</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18266</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12676</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24323</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,71%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>16396</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10830</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>23346</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>32,73%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>21,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22053</t>
+          <t>17492</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15318</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29347</t>
+          <t>25173</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>38448</t>
+          <t>35758</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30215</t>
+          <t>27706</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49151</t>
+          <t>45469</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>121527</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>105283</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>134517</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>61,59%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>53,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>68,17%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>103275</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>71506</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>124489</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>47,92%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>33,18%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>57,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>128643</t>
+          <t>98043</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>112317</t>
+          <t>86395</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>143827</t>
+          <t>108616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>231919</t>
+          <t>219570</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>184357</t>
+          <t>200754</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>256688</t>
+          <t>238146</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>63,68%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>75786</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>62796</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>92030</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38,41%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>31,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>46,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>112262</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>91048</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>144031</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>52,08%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>42,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>66,82%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>84015</t>
+          <t>78597</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68831</t>
+          <t>68024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100341</t>
+          <t>90245</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>196277</t>
+          <t>154383</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171508</t>
+          <t>135807</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>243839</t>
+          <t>173199</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>46,32%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,107 +2092,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>104831</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>93984</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>115730</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>72,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>64,56%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79,49%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>80101</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>71113</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>88176</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>69,35%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>61,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>80056</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>70792</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>87484</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>69,33%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>61,31%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>75,77%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>184887</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>170896</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>199296</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>70,82%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>65,46%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>76,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>115181</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>103655</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>126827</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>72,23%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>65,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>79,53%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>195282</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>181049</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>210142</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>71,02%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>65,84%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>76,42%</t>
         </is>
       </c>
     </row>
@@ -2205,107 +2205,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>40755</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>29856</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>51602</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>27,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,51%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>35,44%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>35408</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>27333</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>44396</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>30,65%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>35410</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>27982</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>44674</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>30,67%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>24,23%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>38,69%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>76165</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>61756</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>90156</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>29,18%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>23,66%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44280</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>32634</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>55806</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>27,77%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>20,47%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>35,0%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>79688</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>64828</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>93921</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>28,98%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>23,58%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>44495</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>37988</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>50910</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>67,56%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>57,68%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>77,3%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>50887</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>44156</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>56172</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>73,86%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>64,09%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>81,53%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>45111</t>
+          <t>52070</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36906</t>
+          <t>45490</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51925</t>
+          <t>57211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>95998</t>
+          <t>96566</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86206</t>
+          <t>86638</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105059</t>
+          <t>105158</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>77,2%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>21368</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>14953</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>27875</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>32,44%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>22,7%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>42,32%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>18008</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>12723</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>24739</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>26,14%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>18,47%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>35,91%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23920</t>
+          <t>18286</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17106</t>
+          <t>13145</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32125</t>
+          <t>24866</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>41927</t>
+          <t>39654</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32866</t>
+          <t>31062</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>49582</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>452060</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>429111</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>474881</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>66,9%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>63,51%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>70,28%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>583</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>397186</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>338272</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>424695</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>61,57%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>52,43%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>65,83%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>485041</t>
+          <t>394305</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>458721</t>
+          <t>372167</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>509971</t>
+          <t>414575</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>882227</t>
+          <t>846365</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>820914</t>
+          <t>816263</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>920713</t>
+          <t>879415</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>68,39%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>223635</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>200814</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>246584</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>33,1%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>29,72%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>36,49%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>247945</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>220436</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>306859</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>38,43%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>34,17%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>47,57%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>247327</t>
+          <t>215927</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>222397</t>
+          <t>195657</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>273647</t>
+          <t>238065</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>495272</t>
+          <t>439562</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>456786</t>
+          <t>406512</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>556585</t>
+          <t>469664</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
